--- a/Excel/LegacyCoreConfig.xlsx
+++ b/Excel/LegacyCoreConfig.xlsx
@@ -27,24 +27,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>ItemId</t>
-  </si>
-  <si>
-    <t>AttrIdList</t>
-  </si>
-  <si>
-    <t>AttrValueList</t>
-  </si>
-  <si>
-    <t>AttrRiseList</t>
+    <t>LevelRequire</t>
+  </si>
+  <si>
+    <t>AttrId</t>
+  </si>
+  <si>
+    <t>AttrValue</t>
+  </si>
+  <si>
+    <t>Fee</t>
   </si>
   <si>
     <t>Id</t>
@@ -53,16 +53,43 @@
     <t>int</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>14,16,15,26</t>
-  </si>
-  <si>
-    <t>100,100,100,100</t>
-  </si>
-  <si>
-    <t>50,50,50,50</t>
+    <t>double</t>
+  </si>
+  <si>
+    <t>幸运</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>物伤加成</t>
+  </si>
+  <si>
+    <t>魔伤加成</t>
+  </si>
+  <si>
+    <t>道伤加成</t>
+  </si>
+  <si>
+    <t>生命倍率</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>物攻倍率</t>
+  </si>
+  <si>
+    <t>魔攻倍率</t>
+  </si>
+  <si>
+    <t>道攻倍率</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
+  </si>
+  <si>
+    <t>增伤倍率</t>
   </si>
 </sst>
 </file>
@@ -98,10 +125,8 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -702,7 +727,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -710,7 +735,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1030,78 +1055,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="5" width="9.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="2" customWidth="1"/>
-    <col min="9" max="16364" width="9" style="2"/>
-    <col min="16365" max="16384" width="9" style="1"/>
+    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.375" style="2" customWidth="1"/>
+    <col min="6" max="7" width="15.125" style="2" customWidth="1"/>
+    <col min="8" max="16363" width="9" style="2"/>
+    <col min="16364" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
+      <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="H2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:8">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:8">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -1117,10 +1141,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1128,19 +1149,19 @@
         <v>1</v>
       </c>
       <c r="D6" s="1">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="4">
-        <v>6000001</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1148,18 +1169,19 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <f t="shared" ref="D7:D17" si="0">D6+10</f>
+        <v>20</v>
       </c>
       <c r="E7" s="4">
-        <v>6000002</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1168,18 +1190,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>6000003</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E8" s="5">
+        <v>33</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1188,19 +1211,20 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>6000003</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="E9" s="5">
+        <v>34</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1208,19 +1232,20 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>6000003</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="E10" s="5">
+        <v>35</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1228,19 +1253,20 @@
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="E11" s="4">
-        <v>6000003</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>11</v>
+        <v>2003</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>6</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1248,19 +1274,20 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>6000003</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2002</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>7</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1268,81 +1295,219 @@
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
-        <v>6000003</v>
-      </c>
-      <c r="F13" s="5" t="s">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2004</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>8</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2005</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>9</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2006</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2001</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2010</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="5:8">
       <c r="E18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="5:5">
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1"/>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="5:8">
       <c r="E20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="5:5">
-      <c r="E32" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1"/>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E22" s="5"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E23" s="5"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E24" s="5"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E25" s="5"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E26" s="5"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E27" s="5"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E28" s="5"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E29" s="5"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E30" s="5"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E31" s="5"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E32" s="5"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E33" s="5"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E34" s="5"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="5:8">
+      <c r="E35" s="5"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" customHeight="1" spans="5:8">
+      <c r="E36" s="5"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" customHeight="1" spans="5:8">
+      <c r="E37" s="5"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:E3 F3:H3 E4 F4:H4 E5 F5:H5 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D3 E3:F3 G3 C4 D4 E4:F4 G4 C5:D5 E5:F5 G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
